--- a/data/trans_dic/IP41-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,86; 81,13</t>
+          <t>65,96; 81,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,03; 86,8</t>
+          <t>73,72; 86,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,25; 88,03</t>
+          <t>71,62; 87,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,83; 88,24</t>
+          <t>74,36; 87,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,47; 86,97</t>
+          <t>73,05; 86,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,3; 77,15</t>
+          <t>57,12; 76,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73,13; 82,91</t>
+          <t>72,62; 83,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75,56; 85,31</t>
+          <t>75,57; 85,6</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67,67; 80,27</t>
+          <t>68,07; 80,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,4; 95,93</t>
+          <t>92,39; 95,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,88; 90,87</t>
+          <t>86,17; 90,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,81; 85,45</t>
+          <t>79,95; 85,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,62; 95,27</t>
+          <t>91,6; 95,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,86; 90,75</t>
+          <t>85,63; 90,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,47; 86,06</t>
+          <t>80,62; 86,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,51; 95,25</t>
+          <t>92,56; 95,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86,84; 90,34</t>
+          <t>86,68; 90,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81,26; 85,15</t>
+          <t>81,02; 84,96</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,15</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,79; 94,49</t>
+          <t>87,74; 94,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,95; 97,22</t>
+          <t>91,81; 97,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,44; 92,74</t>
+          <t>84,74; 92,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,91; 96,93</t>
+          <t>90,78; 96,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,69; 94,98</t>
+          <t>87,35; 95,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,51; 93,1</t>
+          <t>86,18; 93,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,4; 95,17</t>
+          <t>90,45; 95,03</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>91,02; 95,72</t>
+          <t>91,02; 95,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86,16; 91,89</t>
+          <t>86,71; 91,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,41</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,21; 92,68</t>
+          <t>89,09; 92,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,23; 91,04</t>
+          <t>87,17; 90,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,72; 86,33</t>
+          <t>81,58; 86,18</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,57; 93,92</t>
+          <t>90,68; 93,88</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,31; 90,19</t>
+          <t>86,31; 90,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,43; 85,92</t>
+          <t>81,4; 85,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,95</t>
+          <t>90,53; 92,91</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>87,53; 90,04</t>
+          <t>87,39; 90,11</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82,22; 85,45</t>
+          <t>82,43; 85,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,1</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>64547</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74819</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>48390</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71330</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>69586</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46716</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>135877</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>144405</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>95106</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>57217; 70962</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68092; 80257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>42526; 52108</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>64578; 76231</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>62960; 74714</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>39196; 52361</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>126063; 144304</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>134936; 152840</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>87122; 102591</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1174</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>389094</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>400135</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>390480</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>441153</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>437262</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>407339</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>830247</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>837397</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>797820</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>380733; 395580</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>389039; 410165</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>376886; 404677</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>431700; 448269</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>423377; 448020</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>392996; 419902</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>817677; 840555</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>819975; 852728</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>776805; 814665</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>449</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>157832</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158769</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153406</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>148656</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>158384</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>168714</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>306487</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>317153</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>322119</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>151293; 163209</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>153143; 162529</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>146353; 159569</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>143002; 152310</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>150450; 163761</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>161576; 174991</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>298456; 313540</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>308583; 324163</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>312314; 330958</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1909</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1789</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>611473</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>633723</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>592276</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1272611</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1298955</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>1215045</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>598015; 623118</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>619496; 646671</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>573893; 606252</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>648912; 671860</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>649833; 678702</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>605264; 638164</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1255626; 1288520</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>1279025; 1318836</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>1192798; 1236343</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP41-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Estudios-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -519,15 +519,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -538,23 +535,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -576,47 +570,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -632,9 +611,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -664,47 +640,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>80,87%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>74,31%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,96; 81,81</t>
+          <t>66,5; 82,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,72; 86,89</t>
+          <t>73,48; 86,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71,62; 87,76</t>
+          <t>72,41; 88,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74,59; 88,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>74,36; 87,78</t>
+          <t>72,13; 86,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,05; 86,68</t>
+          <t>58,81; 77,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>57,12; 76,31</t>
+          <t>72,57; 82,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>75,89; 85,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>72,62; 83,13</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>75,57; 85,6</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>68,07; 80,15</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>66,84; 80,24</t>
         </is>
       </c>
     </row>
@@ -804,47 +750,32 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88,53%</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
           <t>83,21%</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -857,62 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,39; 95,99</t>
+          <t>92,34; 96,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,17; 90,85</t>
+          <t>86,01; 90,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,95; 85,85</t>
+          <t>79,95; 85,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>91,58; 95,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>91,6; 95,12</t>
+          <t>85,95; 90,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,63; 90,61</t>
+          <t>80,79; 86,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>80,62; 86,14</t>
+          <t>92,65; 95,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>86,62; 90,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>92,56; 95,15</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86,68; 90,15</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>81,02; 84,96</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>81,18; 85,12</t>
         </is>
       </c>
     </row>
@@ -944,47 +860,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>89,43%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -997,62 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,74; 94,65</t>
+          <t>87,35; 94,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,81; 97,43</t>
+          <t>91,72; 97,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,74; 92,4</t>
+          <t>84,33; 92,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,82; 96,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90,78; 96,69</t>
+          <t>87,68; 95,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>87,35; 95,08</t>
+          <t>85,49; 93,12</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,18; 93,33</t>
+          <t>90,39; 95,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,99; 95,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90,45; 95,03</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>91,02; 95,61</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>86,71; 91,88</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>86,19; 91,9</t>
         </is>
       </c>
     </row>
@@ -1084,47 +970,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>88,75%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>83,97%</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,09; 92,83</t>
+          <t>89,0; 92,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,17; 90,99</t>
+          <t>87,29; 91,06</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,58; 86,18</t>
+          <t>81,96; 86,42</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>90,69; 93,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,68; 93,88</t>
+          <t>86,1; 90,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,31; 90,15</t>
+          <t>81,32; 85,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,4; 85,83</t>
+          <t>90,55; 92,83</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>87,42; 90,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90,53; 92,91</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>87,39; 90,11</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>82,43; 85,44</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>82,42; 85,46</t>
         </is>
       </c>
     </row>
@@ -1205,14 +1061,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="K1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1224,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1238,15 +1094,12 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,65%)</t>
+          <t>Adulto que está casado y/o que vive en pareja (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1257,23 +1110,20 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Niño</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="L1" s="3" t="n"/>
-      <c r="M1" s="3" t="n"/>
-      <c r="N1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -1295,47 +1145,32 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
           <t>2007</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>2012</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2007</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
-      <c r="N2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -1351,9 +1186,6 @@
       <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
-      <c r="L3" s="2" t="n"/>
-      <c r="M3" s="2" t="n"/>
-      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1383,47 +1215,32 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>205</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>204</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>204</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
           <t>140</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1451,47 +1268,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>71330</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71330</t>
+          <t>69586</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69586</t>
+          <t>46716</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46716</t>
+          <t>135877</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>144405</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>135877</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>144405</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
           <t>95106</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57217; 70962</t>
+          <t>57687; 71136</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>68092; 80257</t>
+          <t>67874; 80278</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42526; 52108</t>
+          <t>42995; 52715</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64780; 76731</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64578; 76231</t>
+          <t>62173; 74686</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>62960; 74714</t>
+          <t>40349; 53357</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>39196; 52361</t>
+          <t>125976; 143473</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>135509; 152766</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>126063; 144304</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>134936; 152840</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>87122; 102591</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>85552; 102699</t>
         </is>
       </c>
     </row>
@@ -1591,47 +1378,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>664</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>626</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>626</t>
+          <t>580</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>1251</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
           <t>1174</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1659,47 +1431,32 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>441153</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>441153</t>
+          <t>437262</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>437262</t>
+          <t>407339</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>407339</t>
+          <t>830247</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>837397</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>830247</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>837397</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
           <t>797820</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>380733; 395580</t>
+          <t>380509; 395675</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>389039; 410165</t>
+          <t>388338; 409805</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>376886; 404677</t>
+          <t>376890; 403368</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>431575; 448243</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>431700; 448269</t>
+          <t>424978; 448658</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>423377; 448020</t>
+          <t>393815; 421380</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>392996; 419902</t>
+          <t>818420; 840907</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>819335; 852327</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>817677; 840555</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>819975; 852728</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>776805; 814665</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>778414; 816116</t>
         </is>
       </c>
     </row>
@@ -1799,47 +1541,32 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>222</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>245</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>453</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>449</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
           <t>475</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1867,47 +1594,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>148656</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>148656</t>
+          <t>158384</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>158384</t>
+          <t>168714</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>168714</t>
+          <t>306487</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>317153</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>306487</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>317153</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
           <t>322119</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>151293; 163209</t>
+          <t>150614; 163271</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153143; 162529</t>
+          <t>153005; 162534</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146353; 159569</t>
+          <t>145646; 159564</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>143063; 152756</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>143002; 152310</t>
+          <t>151003; 163773</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>150450; 163761</t>
+          <t>160288; 174593</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>161576; 174991</t>
+          <t>298235; 314019</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>308502; 323877</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>298456; 313540</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>308583; 324163</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>312314; 330958</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>310459; 331021</t>
         </is>
       </c>
     </row>
@@ -2007,47 +1704,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>993</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>947</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>893</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>1909</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
           <t>1789</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2075,47 +1757,32 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>661138</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>661138</t>
+          <t>665232</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>665232</t>
+          <t>622770</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>622770</t>
+          <t>1272611</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1298955</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1272611</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1298955</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
           <t>1215045</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -2128,62 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>598015; 623118</t>
+          <t>597408; 622663</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>619496; 646671</t>
+          <t>620351; 647122</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>573893; 606252</t>
+          <t>576591; 607939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>648998; 671824</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>648912; 671860</t>
+          <t>648205; 678540</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>649833; 678702</t>
+          <t>604626; 638256</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>605264; 638164</t>
+          <t>1255897; 1287529</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1279449; 1317524</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1255626; 1288520</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>1279025; 1318836</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>1192798; 1236343</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>1192569; 1236573</t>
         </is>
       </c>
     </row>
@@ -2196,13 +1848,13 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/IP41-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP41-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>82,14%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>80,73%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68,08%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>74,41%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>81,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>81,49%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>82,14%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>80,73%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,5; 82,01</t>
+          <t>74,83; 88,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73,48; 86,91</t>
+          <t>73,47; 86,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,41; 88,78</t>
+          <t>58,3; 77,15</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>74,59; 88,35</t>
+          <t>65,86; 81,13</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,13; 86,65</t>
+          <t>73,03; 86,8</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,81; 77,76</t>
+          <t>72,25; 88,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,57; 82,65</t>
+          <t>73,13; 82,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>75,89; 85,55</t>
+          <t>75,56; 85,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66,84; 80,24</t>
+          <t>67,67; 80,27</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93,61%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>94,42%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>88,63%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>82,84%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>83,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>92,34; 96,02</t>
+          <t>91,62; 95,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86,01; 90,77</t>
+          <t>85,86; 90,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79,95; 85,57</t>
+          <t>80,47; 86,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>91,58; 95,11</t>
+          <t>92,4; 95,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>85,95; 90,74</t>
+          <t>85,88; 90,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,79; 86,45</t>
+          <t>79,81; 85,45</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>92,65; 95,19</t>
+          <t>92,51; 95,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>86,62; 90,1</t>
+          <t>86,84; 90,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>81,18; 85,12</t>
+          <t>81,26; 85,15</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>94,37%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>91,96%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89,98%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>91,53%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>95,18%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>88,83%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94,37%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>87,35; 94,69</t>
+          <t>90,91; 96,93</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91,72; 97,44</t>
+          <t>87,69; 94,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,33; 92,39</t>
+          <t>85,51; 93,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,82; 96,97</t>
+          <t>87,79; 94,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>87,68; 95,09</t>
+          <t>91,95; 97,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 93,12</t>
+          <t>84,44; 92,74</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>90,39; 95,17</t>
+          <t>90,4; 95,17</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,99; 95,53</t>
+          <t>91,02; 95,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,19; 91,9</t>
+          <t>86,16; 91,89</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>92,38%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>83,76%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>91,09%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>89,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>84,19%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>92,38%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>88,36%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>89,0; 92,76</t>
+          <t>90,57; 93,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>87,29; 91,06</t>
+          <t>86,31; 90,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,96; 86,42</t>
+          <t>81,43; 85,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90,69; 93,88</t>
+          <t>89,21; 92,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>86,1; 90,13</t>
+          <t>87,23; 91,04</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,32; 85,84</t>
+          <t>81,72; 86,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,55; 92,83</t>
+          <t>90,55; 92,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>87,42; 90,02</t>
+          <t>87,53; 90,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,42; 85,46</t>
+          <t>82,22; 85,45</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>72</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>71330</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>69586</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46716</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>64547</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>74819</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>48390</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>71330</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>69586</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>46716</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>57687; 71136</t>
+          <t>64985; 76633</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67874; 80278</t>
+          <t>63324; 74964</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42995; 52715</t>
+          <t>40002; 52937</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>64780; 76731</t>
+          <t>57132; 70377</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62173; 74686</t>
+          <t>67459; 80180</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40349; 53357</t>
+          <t>42898; 52272</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>125976; 143473</t>
+          <t>126940; 143925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>135509; 152766</t>
+          <t>134924; 152324</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85552; 102699</t>
+          <t>86608; 102738</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>580</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>587</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>580</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>594</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>441153</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>437262</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>407339</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>389094</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>400135</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>390480</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>441153</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>437262</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>407339</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>380509; 395675</t>
+          <t>431786; 448998</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>388338; 409805</t>
+          <t>424522; 448692</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>376890; 403368</t>
+          <t>392257; 419504</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>431575; 448243</t>
+          <t>380757; 395341</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>424978; 448658</t>
+          <t>387756; 410292</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>393815; 421380</t>
+          <t>376209; 402780</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>818420; 840907</t>
+          <t>817221; 841402</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>819335; 852327</t>
+          <t>821451; 854588</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>778414; 816116</t>
+          <t>779137; 816426</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>224</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>230</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>245</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>148656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>158384</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>168714</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>157832</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>158769</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>153406</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>148656</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>158384</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>168714</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>150614; 163271</t>
+          <t>143202; 152682</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>153005; 162534</t>
+          <t>151033; 163576</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>145646; 159564</t>
+          <t>160332; 174555</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143063; 152756</t>
+          <t>151378; 162931</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>151003; 163773</t>
+          <t>153382; 162178</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>160288; 174593</t>
+          <t>145828; 160160</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>298235; 314019</t>
+          <t>298279; 314023</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>308502; 323877</t>
+          <t>308590; 324525</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>310459; 331021</t>
+          <t>310358; 331001</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>993</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>916</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>912</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>896</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>993</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>893</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>661138</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>665232</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>622770</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>611473</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>633723</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>592276</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>661138</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>665232</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>622770</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>597408; 622663</t>
+          <t>648186; 672164</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>620351; 647122</t>
+          <t>649810; 678994</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>576591; 607939</t>
+          <t>605446; 638865</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>648998; 671824</t>
+          <t>598853; 622097</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>648205; 678540</t>
+          <t>619897; 647022</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>604626; 638256</t>
+          <t>574859; 607310</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1255897; 1287529</t>
+          <t>1255890; 1289194</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1279449; 1317524</t>
+          <t>1281021; 1317721</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1192569; 1236573</t>
+          <t>1189699; 1236418</t>
         </is>
       </c>
     </row>
